--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos.xlsx
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[3, 3, 5, 8, 3]</t>
+          <t>[1, 5, 5, 3, 3]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,94 +472,94 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.05706056535977779</v>
+        <v>0.03988977605246829</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9794605653597779</v>
+        <v>0.9685564427191348</v>
       </c>
       <c r="E2" t="n">
-        <v>63.12</v>
+        <v>121.2</v>
       </c>
       <c r="F2" t="n">
-        <v>49.8</v>
+        <v>84.81999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[3, 5, 3, 5, 5]</t>
+          <t>[8, 9, 4, 4, 6]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5920866427360028</v>
+        <v>0.5066000521040648</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9667533094026695</v>
+        <v>0.9566833854373982</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>88.58</v>
       </c>
       <c r="F3" t="n">
-        <v>34.64</v>
+        <v>80.57000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[1, 4, 3, 6, 5]</t>
+          <t>[3, 1, 6, 6, 9]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.102462667605608</v>
+        <v>0.105087754159701</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9682626676056078</v>
+        <v>0.9639210874930342</v>
       </c>
       <c r="E4" t="n">
-        <v>66.78999999999999</v>
+        <v>123.6</v>
       </c>
       <c r="F4" t="n">
-        <v>45.9</v>
+        <v>78.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[5, 9, 5, 0, 9]</t>
+          <t>[0, 3, 9, 3, 3]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07119494365213337</v>
+        <v>0.0180321925121829</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9584616103188002</v>
+        <v>0.9733655258455161</v>
       </c>
       <c r="E5" t="n">
-        <v>81.38</v>
+        <v>127.48</v>
       </c>
       <c r="F5" t="n">
-        <v>37.79000000000001</v>
+        <v>81.70999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[3, 3, 5, 9, 1]</t>
+          <t>[1, 7, 9, 9, 7]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -568,22 +568,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04690624852942349</v>
+        <v>0.2357607853542195</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9749062485294238</v>
+        <v>0.9539274520208862</v>
       </c>
       <c r="E6" t="n">
-        <v>70.35000000000001</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>45.63</v>
+        <v>95.56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[9, 4, 8, 9, 5]</t>
+          <t>[5, 2, 8, 3, 9]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -592,22 +592,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.06790779758692109</v>
+        <v>0.5441343551163792</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9452411309202542</v>
+        <v>0.941801021783046</v>
       </c>
       <c r="E7" t="n">
-        <v>78.3</v>
+        <v>85.84</v>
       </c>
       <c r="F7" t="n">
-        <v>39.34</v>
+        <v>79.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[2, 4, 0, 3, 3]</t>
+          <t>[2, 5, 4, 6, 0]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -616,190 +616,190 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.09621493599693341</v>
+        <v>0.5986305484174672</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9727482693302668</v>
+        <v>0.9438805484174672</v>
       </c>
       <c r="E8" t="n">
-        <v>69.56</v>
+        <v>94.7</v>
       </c>
       <c r="F8" t="n">
-        <v>44.56</v>
+        <v>69.69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[4, 1, 3, 3, 3]</t>
+          <t>[1, 9, 5, 3, 7]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0434218020956129</v>
+        <v>0.1925623839668568</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9840218020956132</v>
+        <v>0.9509373839668569</v>
       </c>
       <c r="E9" t="n">
-        <v>76.63000000000001</v>
+        <v>97.27000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>42.24</v>
+        <v>92.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[4, 9, 5, 1, 8]</t>
+          <t>[3, 4, 4, 3, 0]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02123417960876369</v>
+        <v>0.1722711847983155</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9594341796087636</v>
+        <v>0.9897295181316487</v>
       </c>
       <c r="E10" t="n">
-        <v>64.41</v>
+        <v>121.81</v>
       </c>
       <c r="F10" t="n">
-        <v>49.5</v>
+        <v>77.69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[2, 9, 3, 4, 5]</t>
+          <t>[4, 4, 2, 3, 7]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.2111634186799115</v>
+        <v>0.3964525250572907</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9614967520132446</v>
+        <v>0.954535858390624</v>
       </c>
       <c r="E11" t="n">
-        <v>75.09999999999999</v>
+        <v>95.38</v>
       </c>
       <c r="F11" t="n">
-        <v>37.45</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[1, 1, 9, 9, 5]</t>
+          <t>[0, 8, 6, 6, 3]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1269212148748576</v>
+        <v>0.05609214982691723</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9538545482081908</v>
+        <v>0.9555504831602505</v>
       </c>
       <c r="E12" t="n">
-        <v>62.97999999999999</v>
+        <v>127.65</v>
       </c>
       <c r="F12" t="n">
-        <v>47.02</v>
+        <v>78.22999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[2, 3, 3, 5, 6]</t>
+          <t>[9, 1, 2, 1, 4]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.09499679778478189</v>
+        <v>0.1363585866035153</v>
       </c>
       <c r="D13" t="n">
-        <v>0.968930131118115</v>
+        <v>0.9813169199368488</v>
       </c>
       <c r="E13" t="n">
-        <v>64.97999999999999</v>
+        <v>107.81</v>
       </c>
       <c r="F13" t="n">
-        <v>47.23</v>
+        <v>89.84</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[3, 5, 2, 1, 3]</t>
+          <t>[5, 9, 4, 7, 5]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2754558505707736</v>
+        <v>0.0576431447168756</v>
       </c>
       <c r="D14" t="n">
-        <v>0.969789183904107</v>
+        <v>0.9601848113835423</v>
       </c>
       <c r="E14" t="n">
-        <v>52.55</v>
+        <v>100.63</v>
       </c>
       <c r="F14" t="n">
-        <v>49.3</v>
+        <v>98.67999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[3, 4, 5, 3, 4]</t>
+          <t>[9, 5, 5, 4, 9]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02172023501942395</v>
+        <v>0.008984590293253584</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9818535683527575</v>
+        <v>0.9651512569599204</v>
       </c>
       <c r="E15" t="n">
-        <v>92.94000000000001</v>
+        <v>95.16000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>33.04</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[9, 2, 9, 5, 9]</t>
+          <t>[1, 1, 0, 3, 4]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -808,46 +808,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.05245958714037507</v>
+        <v>0.6116649030111379</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9435262538070418</v>
+        <v>0.9679149030111378</v>
       </c>
       <c r="E16" t="n">
-        <v>83.72</v>
+        <v>99.14</v>
       </c>
       <c r="F16" t="n">
-        <v>36.5</v>
+        <v>67.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[1, 5, 3, 5, 9]</t>
+          <t>[8, 6, 9, 7, 5]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3649583433876281</v>
+        <v>0.2050786504747403</v>
       </c>
       <c r="D17" t="n">
-        <v>0.965758343387628</v>
+        <v>0.9248703171414071</v>
       </c>
       <c r="E17" t="n">
-        <v>61.99</v>
+        <v>93.77000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>40.83</v>
+        <v>92.86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[9, 9, 5, 3, 8]</t>
+          <t>[7, 0, 2, 5, 0]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -856,22 +856,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1885390776344583</v>
+        <v>0.4251189818551874</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9490057443011247</v>
+        <v>0.9544106485218543</v>
       </c>
       <c r="E18" t="n">
-        <v>69.63999999999999</v>
+        <v>91.17</v>
       </c>
       <c r="F18" t="n">
-        <v>41.03</v>
+        <v>83.38000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[4, 3, 9, 5, 0]</t>
+          <t>[1, 1, 7, 1, 1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -880,214 +880,214 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.1772732904136508</v>
+        <v>0.5314831712531245</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9602732904136508</v>
+        <v>0.9635248379197913</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>94.55</v>
       </c>
       <c r="F19" t="n">
-        <v>36.09</v>
+        <v>75.01000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[9, 4, 4, 2, 5]</t>
+          <t>[1, 6, 0, 1, 4]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.09410076229295264</v>
+        <v>0.156324103001624</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9613007622929524</v>
+        <v>0.9826574363349573</v>
       </c>
       <c r="E20" t="n">
-        <v>83.75999999999999</v>
+        <v>119.48</v>
       </c>
       <c r="F20" t="n">
-        <v>35.76</v>
+        <v>79.97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[9, 4, 9, 1, 9]</t>
+          <t>[8, 4, 3, 9, 7]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1549995090823671</v>
+        <v>0.0292318801663627</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9455995090823671</v>
+        <v>0.9833985468330294</v>
       </c>
       <c r="E21" t="n">
-        <v>83.13</v>
+        <v>111.52</v>
       </c>
       <c r="F21" t="n">
-        <v>33.84</v>
+        <v>93.61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[1, 0, 3, 3, 5]</t>
+          <t>[0, 7, 4, 6, 0]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.2458726011050476</v>
+        <v>0.01779980512004609</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9728726011050479</v>
+        <v>0.9606331384533793</v>
       </c>
       <c r="E22" t="n">
-        <v>56.45</v>
+        <v>117.8</v>
       </c>
       <c r="F22" t="n">
-        <v>47.94</v>
+        <v>88.22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[9, 4, 3, 6, 4]</t>
+          <t>[9, 4, 5, 5, 4]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[3, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1295506739026549</v>
+        <v>0.1158021931573181</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9590173405693214</v>
+        <v>0.9674271931573181</v>
       </c>
       <c r="E23" t="n">
-        <v>86.94</v>
+        <v>96.37</v>
       </c>
       <c r="F23" t="n">
-        <v>32.72</v>
+        <v>98.81999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[3, 5, 3, 4, 4]</t>
+          <t>[4, 5, 0, 8, 8]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.138226213836488</v>
+        <v>0.2626628101218856</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9814928805031545</v>
+        <v>0.9713711434552191</v>
       </c>
       <c r="E24" t="n">
-        <v>84.28</v>
+        <v>93.50999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>34.73</v>
+        <v>92.39000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[1, 6, 3, 3, 3]</t>
+          <t>[4, 4, 7, 5, 9]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.3122530604404832</v>
+        <v>0.06016801147126705</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9688530604404834</v>
+        <v>0.9627096781379335</v>
       </c>
       <c r="E25" t="n">
-        <v>55.73</v>
+        <v>100.63</v>
       </c>
       <c r="F25" t="n">
-        <v>46.26000000000001</v>
+        <v>98.67999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[3, 8, 3, 3, 5]</t>
+          <t>[5, 6, 4, 7, 1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.4638068856350818</v>
+        <v>0.3035723108616629</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9666735523017486</v>
+        <v>0.9621556441949961</v>
       </c>
       <c r="E26" t="n">
-        <v>52.36</v>
+        <v>109.34</v>
       </c>
       <c r="F26" t="n">
-        <v>43.67</v>
+        <v>77.50999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[0, 4, 5, 5, 9]</t>
+          <t>[8, 7, 4, 6, 5]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.09200603211388163</v>
+        <v>0.0488161340006631</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9673393654472151</v>
+        <v>0.9861494673339964</v>
       </c>
       <c r="E27" t="n">
-        <v>81.40000000000001</v>
+        <v>115.28</v>
       </c>
       <c r="F27" t="n">
-        <v>37.42</v>
+        <v>89.78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[8, 3, 4, 5, 1]</t>
+          <t>[0, 3, 4, 3, 2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1096,286 +1096,286 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1554811133625092</v>
+        <v>0.5513302327872209</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9648811133625094</v>
+        <v>0.956580232787221</v>
       </c>
       <c r="E28" t="n">
-        <v>55.77</v>
+        <v>102.06</v>
       </c>
       <c r="F28" t="n">
-        <v>50.82</v>
+        <v>67.77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[9, 5, 6, 3, 5]</t>
+          <t>[9, 8, 7, 7, 4]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.1751230630276447</v>
+        <v>0.04775443438892286</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9555230630276447</v>
+        <v>0.9796294343889229</v>
       </c>
       <c r="E29" t="n">
-        <v>74.42</v>
+        <v>87.63000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>38.76</v>
+        <v>110.19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[5, 5, 3, 0, 1]</t>
+          <t>[5, 4, 3, 2, 0]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.1499477586190261</v>
+        <v>0.0449927092581164</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9692810919523593</v>
+        <v>0.9696177092581164</v>
       </c>
       <c r="E30" t="n">
-        <v>58.85</v>
+        <v>115.45</v>
       </c>
       <c r="F30" t="n">
-        <v>49.27</v>
+        <v>88.89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[4, 1, 9, 9, 5]</t>
+          <t>[1, 4, 2, 4, 2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1988231871534838</v>
+        <v>0.2294681183940632</v>
       </c>
       <c r="D31" t="n">
-        <v>0.952956520486817</v>
+        <v>0.9698847850607299</v>
       </c>
       <c r="E31" t="n">
-        <v>76.89</v>
+        <v>109.02</v>
       </c>
       <c r="F31" t="n">
-        <v>36.48999999999999</v>
+        <v>82.66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[9, 3, 9, 5, 7]</t>
+          <t>[2, 4, 3, 1, 1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1280084856823221</v>
+        <v>0.2884708812166715</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9450751523489889</v>
+        <v>0.9766375478833382</v>
       </c>
       <c r="E32" t="n">
-        <v>73.52</v>
+        <v>112.08</v>
       </c>
       <c r="F32" t="n">
-        <v>40.40000000000001</v>
+        <v>77.23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[3, 9, 1, 9, 4]</t>
+          <t>[7, 0, 7, 4, 6]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.2862611947548938</v>
+        <v>0.2201326574996522</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9480611947548936</v>
+        <v>0.9558409908329858</v>
       </c>
       <c r="E33" t="n">
-        <v>74.48999999999999</v>
+        <v>103.19</v>
       </c>
       <c r="F33" t="n">
-        <v>35.16</v>
+        <v>86.75000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[3, 6, 9, 5, 4]</t>
+          <t>[6, 4, 9, 1, 9]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.1521206501359403</v>
+        <v>0.3167291770541705</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9570539834692738</v>
+        <v>0.9553541770541706</v>
       </c>
       <c r="E34" t="n">
-        <v>80.68000000000001</v>
+        <v>102.33</v>
       </c>
       <c r="F34" t="n">
-        <v>35.74</v>
+        <v>81.56999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[3, 3, 4, 7, 6]</t>
+          <t>[7, 8, 9, 8, 5]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01447586309153481</v>
+        <v>0.2734721219880456</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9677425297582013</v>
+        <v>0.9491387886547124</v>
       </c>
       <c r="E35" t="n">
-        <v>69.67999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="F35" t="n">
-        <v>46.79</v>
+        <v>100.54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[3, 9, 5, 7, 4]</t>
+          <t>[7, 7, 4, 4, 0]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.1505921602817386</v>
+        <v>0.4761763187283671</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9557254936150719</v>
+        <v>0.9596763187283671</v>
       </c>
       <c r="E36" t="n">
-        <v>73.53999999999999</v>
+        <v>84.52</v>
       </c>
       <c r="F36" t="n">
-        <v>40.03</v>
+        <v>85.62</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[2, 9, 3, 1, 4]</t>
+          <t>[7, 8, 8, 1, 6]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.1150695068896849</v>
+        <v>0.1374022505920294</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9627361735563511</v>
+        <v>0.9539022505920296</v>
       </c>
       <c r="E37" t="n">
-        <v>67.44999999999999</v>
+        <v>102.92</v>
       </c>
       <c r="F37" t="n">
-        <v>44.95999999999999</v>
+        <v>91.80000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[2, 1, 9, 5, 3]</t>
+          <t>[9, 6, 5, 6, 1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.1377103974232951</v>
+        <v>0.1581345559798751</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9608437307566284</v>
+        <v>0.9540095559798749</v>
       </c>
       <c r="E38" t="n">
-        <v>61.18999999999999</v>
+        <v>112.35</v>
       </c>
       <c r="F38" t="n">
-        <v>47.98</v>
+        <v>83.48999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[1, 3, 3, 3, 9]</t>
+          <t>[9, 5, 0, 7, 8]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.5538798618209427</v>
+        <v>0.1650413868725632</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9700131951542761</v>
+        <v>0.9455413868725634</v>
       </c>
       <c r="E39" t="n">
-        <v>57.19</v>
+        <v>88.08</v>
       </c>
       <c r="F39" t="n">
-        <v>38.17</v>
+        <v>100.77</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[3, 2, 4, 4, 3]</t>
+          <t>[7, 2, 7, 1, 0]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1384,166 +1384,166 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.3248437437759992</v>
+        <v>0.4887432537349241</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9709104104426659</v>
+        <v>0.9458265870682575</v>
       </c>
       <c r="E40" t="n">
-        <v>72.72</v>
+        <v>86.53999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>35.75</v>
+        <v>82.52000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[3, 1, 7, 5, 3]</t>
+          <t>[4, 3, 4, 2, 7]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.2177892399900755</v>
+        <v>0.3960245759742227</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9669225733234091</v>
+        <v>0.9541079093075561</v>
       </c>
       <c r="E41" t="n">
-        <v>50.99</v>
+        <v>95.38</v>
       </c>
       <c r="F41" t="n">
-        <v>51.88000000000001</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[3, 4, 8, 3, 3]</t>
+          <t>[6, 1, 1, 4, 6]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.03573437102840191</v>
+        <v>0.6891193928140502</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9826677043617351</v>
+        <v>0.9546193928140502</v>
       </c>
       <c r="E42" t="n">
-        <v>69.38</v>
+        <v>101.24</v>
       </c>
       <c r="F42" t="n">
-        <v>46.78</v>
+        <v>59.46</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[3, 4, 9, 3, 0]</t>
+          <t>[3, 4, 4, 9, 2]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.2715883376819569</v>
+        <v>0.1281979995039653</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9622550043486234</v>
+        <v>0.988864666170632</v>
       </c>
       <c r="E43" t="n">
-        <v>76.59999999999999</v>
+        <v>108.76</v>
       </c>
       <c r="F43" t="n">
-        <v>34.76</v>
+        <v>90.06999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[5, 3, 1, 0, 4]</t>
+          <t>[6, 7, 3, 4, 9]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.1274122404705401</v>
+        <v>0.3427847156257168</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9712789071372067</v>
+        <v>0.9579097156257169</v>
       </c>
       <c r="E44" t="n">
-        <v>65.11</v>
+        <v>108.09</v>
       </c>
       <c r="F44" t="n">
-        <v>46.25</v>
+        <v>75.84</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[4, 3, 4, 0, 9]</t>
+          <t>[4, 9, 4, 9, 9]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.1634020454396646</v>
+        <v>0.1973692629360915</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9709353787729977</v>
+        <v>0.9653275962694249</v>
       </c>
       <c r="E45" t="n">
-        <v>85.25999999999999</v>
+        <v>87.89000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>33.07</v>
+        <v>100.16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[9, 5, 4, 3, 0]</t>
+          <t>[4, 1, 4, 8, 9]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.1772732904136508</v>
+        <v>0.1882240312025883</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9602732904136508</v>
+        <v>0.990015697869255</v>
       </c>
       <c r="E46" t="n">
-        <v>79</v>
+        <v>99.25</v>
       </c>
       <c r="F46" t="n">
-        <v>36.09</v>
+        <v>93.67</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[8, 5, 3, 6, 3]</t>
+          <t>[3, 0, 5, 3, 4]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1552,46 +1552,46 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.08993972207668879</v>
+        <v>0.6315399423731777</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9620730554100222</v>
+        <v>0.9538732757065113</v>
       </c>
       <c r="E47" t="n">
-        <v>59.54</v>
+        <v>98.00000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>50.44</v>
+        <v>65.84</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[9, 2, 3, 6, 3]</t>
+          <t>[8, 8, 7, 4, 4]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.04906202707460241</v>
+        <v>0.09919690916519823</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9594620270746024</v>
+        <v>0.9816969091651981</v>
       </c>
       <c r="E48" t="n">
-        <v>71.22</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>44.58</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[3, 5, 3, 0, 3]</t>
+          <t>[3, 0, 4, 0, 6]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1600,64 +1600,64 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.02695571397432474</v>
+        <v>0.2960306847967176</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9838223806409917</v>
+        <v>0.9815306847967177</v>
       </c>
       <c r="E49" t="n">
-        <v>72.46000000000001</v>
+        <v>115.72</v>
       </c>
       <c r="F49" t="n">
-        <v>45.23</v>
+        <v>74.34</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[5, 4, 5, 9, 7]</t>
+          <t>[5, 3, 5, 5, 9]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.05952463666937676</v>
+        <v>0.1733990178427788</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9569913033360431</v>
+        <v>0.9649823511761124</v>
       </c>
       <c r="E50" t="n">
-        <v>75.93999999999998</v>
+        <v>101.58</v>
       </c>
       <c r="F50" t="n">
-        <v>41.36</v>
+        <v>91.31</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[6, 3, 4, 1, 9]</t>
+          <t>[8, 4, 9, 8, 9]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.06469133866971678</v>
+        <v>0.01548362045957345</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9669580053363838</v>
+        <v>0.9843586204595732</v>
       </c>
       <c r="E51" t="n">
-        <v>73.03</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>43.25000000000001</v>
+        <v>111.12</v>
       </c>
     </row>
   </sheetData>
